--- a/Financial_Dashboard_Template_Full.xlsx
+++ b/Financial_Dashboard_Template_Full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365cmu-my.sharepoint.com/personal/kanyaphak_su_cmu_ac_th/Documents/KANYAPHAK/07 นำเสนอข้อมูล กบว/00-นำเสนอข้อมูล/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE97AA86-6E20-4838-8F17-CAF079CD92B4}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C4A501-E743-4EF0-9AD1-2680BFDEE476}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -816,20 +816,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -841,6 +827,20 @@
     <xf numFmtId="164" fontId="13" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1136,307 +1136,322 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
     </row>
     <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="B19:H19"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C28:H28"/>
@@ -1446,21 +1461,6 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C7:H7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1479,13 +1479,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1652,12 +1652,12 @@
       <c r="D27" s="6"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1687,32 +1687,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="5" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -1767,20 +1767,18 @@
       <c r="F6" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="11">
-        <v>118940185</v>
-      </c>
+      <c r="G6" s="11"/>
       <c r="H6" s="12">
         <v>51296036.469999999</v>
       </c>
       <c r="I6" s="13"/>
-      <c r="J6" s="14">
+      <c r="J6" s="14" t="str">
         <f t="shared" ref="J6:J36" si="1">IF(G6="","",IFERROR(G6-H6-I6,0))</f>
-        <v>67644148.530000001</v>
-      </c>
-      <c r="K6" s="15">
+        <v/>
+      </c>
+      <c r="K6" s="15" t="str">
         <f t="shared" ref="K6:K36" si="2">IF(OR(G6="",G6=0),"",H6/G6)</f>
-        <v>0.43127590956748552</v>
+        <v/>
       </c>
       <c r="L6" s="16"/>
     </row>
@@ -1898,22 +1896,22 @@
         <f>IF(D10="","",Master_Data!$C$3)</f>
         <v>2569</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="32">
         <v>5700000</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="33">
         <v>964448.65</v>
       </c>
-      <c r="I10" s="42"/>
+      <c r="I10" s="34"/>
       <c r="J10" s="14">
         <f t="shared" si="1"/>
         <v>4735551.3499999996</v>
@@ -1933,22 +1931,22 @@
         <f>IF(D11="","",Master_Data!$C$3)</f>
         <v>2569</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="32">
         <v>51300000</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="33">
         <v>8773832.0999999996</v>
       </c>
-      <c r="I11" s="42"/>
+      <c r="I11" s="34"/>
       <c r="J11" s="14">
         <f t="shared" si="1"/>
         <v>42526167.899999999</v>
@@ -1968,22 +1966,22 @@
         <f>IF(D12="","",Master_Data!$C$3)</f>
         <v>2569</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="32">
         <v>40000</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="33">
         <v>40000</v>
       </c>
-      <c r="I12" s="42"/>
+      <c r="I12" s="34"/>
       <c r="J12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2003,22 +2001,22 @@
         <f>IF(D13="","",Master_Data!$C$3)</f>
         <v>2569</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="32">
         <v>15000000</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="33">
         <v>2112000</v>
       </c>
-      <c r="I13" s="42"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="14">
         <f t="shared" si="1"/>
         <v>12888000</v>
@@ -6805,16 +6803,16 @@
       <c r="L204" s="16"/>
     </row>
     <row r="205" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="35" t="s">
+      <c r="B205" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C205" s="35"/>
-      <c r="D205" s="35"/>
-      <c r="E205" s="35"/>
-      <c r="F205" s="35"/>
+      <c r="C205" s="40"/>
+      <c r="D205" s="40"/>
+      <c r="E205" s="40"/>
+      <c r="F205" s="40"/>
       <c r="G205" s="18">
         <f>SUM(G6:G204)</f>
-        <v>197842561.17000002</v>
+        <v>78902376.170000002</v>
       </c>
       <c r="H205" s="18">
         <f>SUM(H6:H204)</f>
@@ -6826,11 +6824,11 @@
       </c>
       <c r="J205" s="18">
         <f>SUM(J6:J204)</f>
-        <v>130583867.78</v>
+        <v>62939719.25</v>
       </c>
       <c r="K205" s="19">
         <f>IF(G205=0,0,H205/G205)</f>
-        <v>0.33996068890458142</v>
+        <v>0.85242925061074237</v>
       </c>
       <c r="L205" s="20"/>
     </row>
@@ -6884,30 +6882,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="5" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -11872,13 +11870,13 @@
       <c r="K205" s="16"/>
     </row>
     <row r="206" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="35" t="s">
+      <c r="B206" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C206" s="35"/>
-      <c r="D206" s="35"/>
-      <c r="E206" s="35"/>
-      <c r="F206" s="35"/>
+      <c r="C206" s="40"/>
+      <c r="D206" s="40"/>
+      <c r="E206" s="40"/>
+      <c r="F206" s="40"/>
       <c r="G206" s="18">
         <f>SUM(G6:G205)</f>
         <v>176659376</v>
@@ -11942,28 +11940,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -12337,10 +12335,10 @@
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="36"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="18">
         <f>SUM(D7:D18)</f>
         <v>158000000</v>
@@ -12415,21 +12413,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
     </row>
     <row r="5" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -12448,7 +12446,7 @@
       </c>
       <c r="C6" s="14">
         <f>SUM(รายการรายรับ!G6:G204)</f>
-        <v>197842561.17000002</v>
+        <v>78902376.170000002</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>134</v>
@@ -12484,7 +12482,7 @@
       </c>
       <c r="C9" s="14">
         <f>SUM(รายการรายรับ!J6:J204)</f>
-        <v>130583867.78</v>
+        <v>62939719.25</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>134</v>
@@ -12496,18 +12494,18 @@
       </c>
       <c r="C10" s="15">
         <f>IF(SUM(รายการรายรับ!G6:G204)=0,0,SUM(รายการรายรับ!H6:H204)/SUM(รายการรายรับ!G6:G204))</f>
-        <v>0.33996068890458142</v>
+        <v>0.85242925061074237</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -12569,14 +12567,14 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
     </row>
     <row r="20" spans="2:7" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -12607,7 +12605,7 @@
       </c>
       <c r="D21" s="14">
         <f>SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>118940185</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
@@ -12619,7 +12617,7 @@
       </c>
       <c r="G21" s="14">
         <f>SUMIFS(รายการรายรับ!J6:J204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>67644148.530000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -12887,13 +12885,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
@@ -13693,13 +13691,13 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="37" t="s">
+      <c r="B76" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
@@ -13736,7 +13734,7 @@
       </c>
       <c r="F78" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B78)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B78),0)</f>
-        <v>0.44012150567570196</v>
+        <v>8.068402440841421</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
@@ -13782,14 +13780,14 @@
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="37" t="s">
+      <c r="B82" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="37"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">

--- a/Financial_Dashboard_Template_Full.xlsx
+++ b/Financial_Dashboard_Template_Full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365cmu-my.sharepoint.com/personal/kanyaphak_su_cmu_ac_th/Documents/KANYAPHAK/07 นำเสนอข้อมูล กบว/00-นำเสนอข้อมูล/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C4A501-E743-4EF0-9AD1-2680BFDEE476}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A552E6-B272-4ACB-8103-E00096C2D66A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -526,11 +526,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00;[Red]\(#,##0.00\);\-"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]\(0.00%\);\-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,83 +544,97 @@
       <sz val="16"/>
       <color rgb="FF1F3864"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF595959"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F3864"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF7F7F7F"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF7F7F7F"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="16">
@@ -738,10 +753,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -827,6 +843,15 @@
     <xf numFmtId="164" fontId="13" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -841,8 +866,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -924,6 +951,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1136,304 +1167,304 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
     </row>
     <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1479,13 +1510,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1509,7 +1540,7 @@
       </c>
       <c r="C5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46181</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1652,12 +1683,12 @@
       <c r="D27" s="6"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1687,32 +1718,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
     </row>
     <row r="5" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -1767,18 +1798,21 @@
       <c r="F6" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11">
+        <v>118940185</v>
+      </c>
       <c r="H6" s="12">
-        <v>51296036.469999999</v>
+        <f>51296036.47+4806220</f>
+        <v>56102256.469999999</v>
       </c>
       <c r="I6" s="13"/>
-      <c r="J6" s="14" t="str">
+      <c r="J6" s="14">
         <f t="shared" ref="J6:J36" si="1">IF(G6="","",IFERROR(G6-H6-I6,0))</f>
-        <v/>
-      </c>
-      <c r="K6" s="15" t="str">
+        <v>62837928.530000001</v>
+      </c>
+      <c r="K6" s="15">
         <f t="shared" ref="K6:K36" si="2">IF(OR(G6="",G6=0),"",H6/G6)</f>
-        <v/>
+        <v>0.4716846242504163</v>
       </c>
       <c r="L6" s="16"/>
     </row>
@@ -1871,10 +1905,11 @@
         <v>84</v>
       </c>
       <c r="G9" s="11">
-        <v>3572376.17</v>
+        <v>4627281.4000000004</v>
       </c>
       <c r="H9" s="12">
-        <v>3572376.17</v>
+        <f>3572376.17+1054905.23</f>
+        <v>4627281.4000000004</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="14">
@@ -1943,17 +1978,20 @@
       <c r="G11" s="32">
         <v>51300000</v>
       </c>
-      <c r="H11" s="33">
-        <v>8773832.0999999996</v>
-      </c>
-      <c r="I11" s="34"/>
+      <c r="H11" s="35">
+        <v>10849662.1</v>
+      </c>
+      <c r="I11" s="36">
+        <f>20946148.07-10849662.1</f>
+        <v>10096485.970000001</v>
+      </c>
       <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v>42526167.899999999</v>
+        <v>30353851.93</v>
       </c>
       <c r="K11" s="15">
         <f t="shared" si="2"/>
-        <v>0.17102986549707602</v>
+        <v>0.21149438791423</v>
       </c>
       <c r="L11" s="16"/>
     </row>
@@ -1978,7 +2016,7 @@
       <c r="G12" s="32">
         <v>40000</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="35">
         <v>40000</v>
       </c>
       <c r="I12" s="34"/>
@@ -2016,10 +2054,13 @@
       <c r="H13" s="33">
         <v>2112000</v>
       </c>
-      <c r="I13" s="34"/>
+      <c r="I13" s="36">
+        <f>4080000-2112000</f>
+        <v>1968000</v>
+      </c>
       <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v>12888000</v>
+        <v>10920000</v>
       </c>
       <c r="K13" s="15">
         <f t="shared" si="2"/>
@@ -6803,32 +6844,32 @@
       <c r="L204" s="16"/>
     </row>
     <row r="205" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="40" t="s">
+      <c r="B205" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="C205" s="40"/>
-      <c r="D205" s="40"/>
-      <c r="E205" s="40"/>
-      <c r="F205" s="40"/>
+      <c r="C205" s="43"/>
+      <c r="D205" s="43"/>
+      <c r="E205" s="43"/>
+      <c r="F205" s="43"/>
       <c r="G205" s="18">
         <f>SUM(G6:G204)</f>
-        <v>78902376.170000002</v>
+        <v>198897466.40000001</v>
       </c>
       <c r="H205" s="18">
         <f>SUM(H6:H204)</f>
-        <v>67258693.390000001</v>
+        <v>75195648.61999999</v>
       </c>
       <c r="I205" s="18">
         <f>SUM(I6:I204)</f>
-        <v>0</v>
+        <v>12064485.970000001</v>
       </c>
       <c r="J205" s="18">
         <f>SUM(J6:J204)</f>
-        <v>62939719.25</v>
+        <v>111637331.81</v>
       </c>
       <c r="K205" s="19">
         <f>IF(G205=0,0,H205/G205)</f>
-        <v>0.85242925061074237</v>
+        <v>0.37806237545919785</v>
       </c>
       <c r="L205" s="20"/>
     </row>
@@ -6861,7 +6902,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6882,30 +6923,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="5" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -6961,15 +7002,16 @@
         <v>5000000</v>
       </c>
       <c r="H6" s="22">
-        <v>282300</v>
+        <f>282300+197651</f>
+        <v>479951</v>
       </c>
       <c r="I6" s="14">
         <f>IF(G6="","",G6-H6)</f>
-        <v>4717700</v>
+        <v>4520049</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" ref="J6:J37" si="1">IF(OR(G6="",G6=0),"",H6/G6)</f>
-        <v>5.6460000000000003E-2</v>
+        <v>9.5990199999999998E-2</v>
       </c>
       <c r="K6" s="16"/>
     </row>
@@ -7029,15 +7071,16 @@
         <v>13923800</v>
       </c>
       <c r="H8" s="22">
-        <v>4970063.97</v>
+        <f>4970063.97+708801</f>
+        <v>5678864.9699999997</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="2"/>
-        <v>8953736.0300000012</v>
+        <v>8244935.0300000003</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>0.35694738289834671</v>
+        <v>0.4078530982921329</v>
       </c>
       <c r="K8" s="16"/>
     </row>
@@ -7063,15 +7106,16 @@
         <v>3589000</v>
       </c>
       <c r="H9" s="22">
-        <v>2223530.96</v>
+        <f>2223530.96+322175.15</f>
+        <v>2545706.11</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" si="2"/>
-        <v>1365469.04</v>
+        <v>1043293.8900000001</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>0.61954052939537474</v>
+        <v>0.70930791585399833</v>
       </c>
       <c r="K9" s="16"/>
     </row>
@@ -7097,15 +7141,16 @@
         <v>3886800</v>
       </c>
       <c r="H10" s="22">
-        <v>2750721.94</v>
+        <f>2750721.94+351900</f>
+        <v>3102621.94</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" si="2"/>
-        <v>1136078.06</v>
+        <v>784178.06</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>0.7077086394977874</v>
+        <v>0.7982458423381702</v>
       </c>
       <c r="K10" s="16"/>
     </row>
@@ -7131,15 +7176,16 @@
         <v>1417200</v>
       </c>
       <c r="H11" s="22">
-        <v>899200</v>
+        <f>899200+114600</f>
+        <v>1013800</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" si="2"/>
-        <v>518000</v>
+        <v>403400</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>0.63449054473609934</v>
+        <v>0.71535421958791989</v>
       </c>
       <c r="K11" s="16"/>
     </row>
@@ -7165,15 +7211,16 @@
         <v>35358600</v>
       </c>
       <c r="H12" s="22">
-        <v>10415453.76</v>
+        <f>10415453.76+2617685.87</f>
+        <v>13033139.629999999</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" si="2"/>
-        <v>24943146.240000002</v>
+        <v>22325460.370000001</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>0.29456635047767726</v>
+        <v>0.36859885940054182</v>
       </c>
       <c r="K12" s="16"/>
     </row>
@@ -7199,15 +7246,16 @@
         <v>3374000</v>
       </c>
       <c r="H13" s="22">
-        <v>266395.61</v>
+        <f>266395.61+111617.85</f>
+        <v>378013.45999999996</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" si="2"/>
-        <v>3107604.39</v>
+        <v>2995986.54</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>7.8955426793123881E-2</v>
+        <v>0.11203718435091878</v>
       </c>
       <c r="K13" s="16"/>
     </row>
@@ -7233,15 +7281,16 @@
         <v>33660976</v>
       </c>
       <c r="H14" s="22">
-        <v>7274659.4000000004</v>
+        <f>7274659.4+2995408.66</f>
+        <v>10270068.060000001</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="2"/>
-        <v>26386316.600000001</v>
+        <v>23390907.939999998</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>0.21611552202170253</v>
+        <v>0.30510309802068725</v>
       </c>
       <c r="K14" s="16"/>
     </row>
@@ -7300,16 +7349,16 @@
       <c r="G16" s="21">
         <v>2168000</v>
       </c>
-      <c r="H16" s="22">
-        <v>328849.34999999998</v>
+      <c r="H16" s="37">
+        <v>455424.65</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="2"/>
-        <v>1839150.65</v>
+        <v>1712575.35</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>0.1516832795202952</v>
+        <v>0.21006672047970482</v>
       </c>
       <c r="K16" s="16"/>
     </row>
@@ -7334,16 +7383,16 @@
       <c r="G17" s="21">
         <v>49500000</v>
       </c>
-      <c r="H17" s="22">
-        <v>4106698.88</v>
+      <c r="H17" s="37">
+        <v>5824865.4199999999</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" si="2"/>
-        <v>45393301.119999997</v>
+        <v>43675134.579999998</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>8.2963613737373737E-2</v>
+        <v>0.11767404888888888</v>
       </c>
       <c r="K17" s="16"/>
     </row>
@@ -7368,16 +7417,16 @@
       <c r="G18" s="21">
         <v>15000000</v>
       </c>
-      <c r="H18" s="22">
-        <v>606970</v>
+      <c r="H18" s="37">
+        <v>1054302.77</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" si="2"/>
-        <v>14393030</v>
+        <v>13945697.23</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>4.046466666666667E-2</v>
+        <v>7.0286851333333331E-2</v>
       </c>
       <c r="K18" s="16"/>
     </row>
@@ -11870,28 +11919,28 @@
       <c r="K205" s="16"/>
     </row>
     <row r="206" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="40" t="s">
+      <c r="B206" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="C206" s="40"/>
-      <c r="D206" s="40"/>
-      <c r="E206" s="40"/>
-      <c r="F206" s="40"/>
+      <c r="C206" s="43"/>
+      <c r="D206" s="43"/>
+      <c r="E206" s="43"/>
+      <c r="F206" s="43"/>
       <c r="G206" s="18">
         <f>SUM(G6:G205)</f>
         <v>176659376</v>
       </c>
       <c r="H206" s="18">
         <f>SUM(H6:H205)</f>
-        <v>34816506.370000005</v>
+        <v>44528420.510000005</v>
       </c>
       <c r="I206" s="18">
         <f>SUM(I6:I205)</f>
-        <v>141842869.63000003</v>
+        <v>132130955.48999999</v>
       </c>
       <c r="J206" s="19">
         <f>IF(G206=0,0,H206/G206)</f>
-        <v>0.19708269755237903</v>
+        <v>0.25205806517736146</v>
       </c>
       <c r="K206" s="20"/>
     </row>
@@ -11930,40 +11979,42 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:V19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="9" width="18" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+    <row r="2" spans="2:22" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B3" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>73</v>
       </c>
@@ -11972,7 +12023,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>107</v>
       </c>
@@ -11998,231 +12049,263 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="7">
         <v>10</v>
       </c>
       <c r="C7" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="25">
-        <v>7000000</v>
-      </c>
-      <c r="E7" s="21">
-        <v>13000000</v>
-      </c>
-      <c r="F7" s="26">
-        <v>144000000</v>
-      </c>
-      <c r="G7" s="26">
-        <v>28000000</v>
+      <c r="D7" s="46">
+        <v>6975741.9900000002</v>
+      </c>
+      <c r="E7" s="46">
+        <v>13400251.43</v>
+      </c>
+      <c r="F7" s="46">
+        <v>144393405.75</v>
+      </c>
+      <c r="G7" s="46">
+        <v>27674990.490000002</v>
       </c>
       <c r="H7" s="14">
-        <f t="shared" ref="H7:H19" si="0">D7-E7</f>
-        <v>-6000000</v>
+        <f>D7-E7</f>
+        <v>-6424509.4399999995</v>
       </c>
       <c r="I7" s="14">
-        <f t="shared" ref="I7:I19" si="1">F7+G7</f>
-        <v>172000000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+        <f>F7+G7</f>
+        <v>172068396.24000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" s="7">
         <v>11</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="25">
-        <v>1000000</v>
-      </c>
-      <c r="E8" s="21">
-        <v>26000000</v>
-      </c>
-      <c r="F8" s="26">
-        <v>134000000</v>
-      </c>
-      <c r="G8" s="26">
-        <v>29000000</v>
+      <c r="D8" s="46">
+        <v>6865514.4200000009</v>
+      </c>
+      <c r="E8" s="46">
+        <v>17135897.079999998</v>
+      </c>
+      <c r="F8" s="46">
+        <v>134277439.19999999</v>
+      </c>
+      <c r="G8" s="46">
+        <v>27520574.380000003</v>
       </c>
       <c r="H8" s="14">
-        <f t="shared" si="0"/>
-        <v>-25000000</v>
+        <f t="shared" ref="H7:H19" si="0">D8-E8</f>
+        <v>-10270382.659999996</v>
       </c>
       <c r="I8" s="14">
-        <f t="shared" si="1"/>
-        <v>163000000</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+        <f t="shared" ref="I7:I19" si="1">F8+G8</f>
+        <v>161798013.57999998</v>
+      </c>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="7">
         <v>12</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="25">
-        <v>6000000</v>
-      </c>
-      <c r="E9" s="21">
-        <v>12000000</v>
-      </c>
-      <c r="F9" s="26">
-        <v>128000000</v>
-      </c>
-      <c r="G9" s="26">
-        <v>29000000</v>
+      <c r="D9" s="46">
+        <v>5731449.7199999997</v>
+      </c>
+      <c r="E9" s="46">
+        <v>12260580.720000001</v>
+      </c>
+      <c r="F9" s="46">
+        <v>125158082.45999999</v>
+      </c>
+      <c r="G9" s="46">
+        <v>30110800.120000001</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" si="0"/>
-        <v>-6000000</v>
+        <v>-6529131.0000000009</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" si="1"/>
-        <v>157000000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+        <v>155268882.57999998</v>
+      </c>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>1</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="25">
-        <v>5000000</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8000000</v>
-      </c>
-      <c r="F10" s="26">
-        <v>124000000</v>
-      </c>
-      <c r="G10" s="26">
-        <v>30000000</v>
+      <c r="D10" s="46">
+        <v>14499881.639999999</v>
+      </c>
+      <c r="E10" s="46">
+        <v>15364980.280000001</v>
+      </c>
+      <c r="F10" s="46">
+        <v>124944320.27</v>
+      </c>
+      <c r="G10" s="46">
+        <v>29459463.669999998</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" si="0"/>
-        <v>-3000000</v>
+        <v>-865098.64000000246</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" si="1"/>
-        <v>154000000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+        <v>154403783.94</v>
+      </c>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="7">
         <v>2</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="25">
-        <v>1000000</v>
-      </c>
-      <c r="E11" s="21">
-        <v>3000000</v>
-      </c>
-      <c r="F11" s="26">
-        <v>123000000</v>
-      </c>
-      <c r="G11" s="26">
-        <v>29000000</v>
+      <c r="D11" s="46">
+        <v>4235099.5600000005</v>
+      </c>
+      <c r="E11" s="46">
+        <v>9296265.4499999993</v>
+      </c>
+      <c r="F11" s="46">
+        <v>119987619.17</v>
+      </c>
+      <c r="G11" s="46">
+        <v>29354998.879999995</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" si="0"/>
-        <v>-2000000</v>
+        <v>-5061165.8899999987</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" si="1"/>
-        <v>152000000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+        <v>149342618.05000001</v>
+      </c>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
         <v>3</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="25">
-        <v>22000000</v>
-      </c>
-      <c r="E12" s="21">
-        <v>9000000</v>
-      </c>
-      <c r="F12" s="26">
-        <v>136000000</v>
-      </c>
-      <c r="G12" s="26">
-        <v>29000000</v>
+      <c r="D12" s="46">
+        <v>25255972.079999998</v>
+      </c>
+      <c r="E12" s="46">
+        <v>10838931.229999999</v>
+      </c>
+      <c r="F12" s="46">
+        <v>134589258.44</v>
+      </c>
+      <c r="G12" s="46">
+        <v>29170400.459999993</v>
       </c>
       <c r="H12" s="14">
         <f t="shared" si="0"/>
-        <v>13000000</v>
+        <v>14417040.85</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" si="1"/>
-        <v>165000000</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+        <v>163759658.89999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>4</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="25">
-        <v>19000000</v>
-      </c>
-      <c r="E13" s="21">
-        <v>3000000</v>
-      </c>
-      <c r="F13" s="26">
-        <v>152000000</v>
-      </c>
-      <c r="G13" s="26">
-        <v>28000000</v>
+      <c r="D13" s="46">
+        <v>21050413.659999996</v>
+      </c>
+      <c r="E13" s="46">
+        <v>5892404.5199999996</v>
+      </c>
+      <c r="F13" s="46">
+        <v>149087761.18000001</v>
+      </c>
+      <c r="G13" s="46">
+        <v>29829906.859999992</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" si="0"/>
-        <v>16000000</v>
+        <v>15158009.139999997</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" si="1"/>
-        <v>180000000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+        <v>178917668.03999999</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
         <v>5</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="25">
-        <v>3000000</v>
-      </c>
-      <c r="E14" s="21">
-        <v>10000000</v>
-      </c>
-      <c r="F14" s="26">
-        <v>140000000</v>
-      </c>
-      <c r="G14" s="26">
-        <v>33000000</v>
+      <c r="D14" s="46">
+        <v>15109798.050000001</v>
+      </c>
+      <c r="E14" s="46">
+        <v>15983680.49</v>
+      </c>
+      <c r="F14" s="46">
+        <v>149154182.69</v>
+      </c>
+      <c r="G14" s="46">
+        <v>28889602.909999989</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="0"/>
-        <v>-7000000</v>
+        <v>-873882.43999999948</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="1"/>
-        <v>173000000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+        <v>178043785.59999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="7">
         <v>6</v>
       </c>
@@ -12250,7 +12333,7 @@
         <v>167000000</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="7">
         <v>7</v>
       </c>
@@ -12335,17 +12418,17 @@
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="41"/>
+      <c r="C19" s="44"/>
       <c r="D19" s="18">
         <f>SUM(D7:D18)</f>
-        <v>158000000</v>
+        <v>193723871.12</v>
       </c>
       <c r="E19" s="18">
         <f>SUM(E7:E18)</f>
-        <v>124000000</v>
+        <v>140172991.19999999</v>
       </c>
       <c r="F19" s="18">
         <f>F18</f>
@@ -12357,7 +12440,7 @@
       </c>
       <c r="H19" s="18">
         <f t="shared" si="0"/>
-        <v>34000000</v>
+        <v>53550879.920000017</v>
       </c>
       <c r="I19" s="18">
         <f t="shared" si="1"/>
@@ -12370,7 +12453,7 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B19:C19"/>
   </mergeCells>
-  <conditionalFormatting sqref="F7:F18">
+  <conditionalFormatting sqref="F15:F18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -12382,7 +12465,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G18">
+  <conditionalFormatting sqref="G15:G18">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -12413,21 +12496,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -12446,7 +12529,7 @@
       </c>
       <c r="C6" s="14">
         <f>SUM(รายการรายรับ!G6:G204)</f>
-        <v>78902376.170000002</v>
+        <v>198897466.40000001</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>134</v>
@@ -12458,7 +12541,7 @@
       </c>
       <c r="C7" s="14">
         <f>SUM(รายการรายรับ!H6:H204)</f>
-        <v>67258693.390000001</v>
+        <v>75195648.61999999</v>
       </c>
       <c r="D7" s="28" t="s">
         <v>134</v>
@@ -12470,7 +12553,7 @@
       </c>
       <c r="C8" s="14">
         <f>SUM(รายการรายรับ!I6:I204)</f>
-        <v>0</v>
+        <v>12064485.970000001</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>134</v>
@@ -12482,7 +12565,7 @@
       </c>
       <c r="C9" s="14">
         <f>SUM(รายการรายรับ!J6:J204)</f>
-        <v>62939719.25</v>
+        <v>111637331.81</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>134</v>
@@ -12494,18 +12577,18 @@
       </c>
       <c r="C10" s="15">
         <f>IF(SUM(รายการรายรับ!G6:G204)=0,0,SUM(รายการรายรับ!H6:H204)/SUM(รายการรายรับ!G6:G204))</f>
-        <v>0.85242925061074237</v>
+        <v>0.37806237545919785</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -12536,7 +12619,7 @@
       </c>
       <c r="C15" s="14">
         <f>SUM(รายการค่าใช้จ่าย!H6:H205)</f>
-        <v>34816506.370000005</v>
+        <v>44528420.510000005</v>
       </c>
       <c r="D15" s="28" t="s">
         <v>134</v>
@@ -12548,7 +12631,7 @@
       </c>
       <c r="C16" s="14">
         <f>SUM(รายการค่าใช้จ่าย!G6:G205)-SUM(รายการค่าใช้จ่าย!H6:H205)</f>
-        <v>141842869.63</v>
+        <v>132130955.48999999</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>134</v>
@@ -12560,21 +12643,21 @@
       </c>
       <c r="C17" s="15">
         <f>IF(SUM(รายการค่าใช้จ่าย!G6:G205)=0,0,SUM(รายการค่าใช้จ่าย!H6:H205)/SUM(รายการค่าใช้จ่าย!G6:G205))</f>
-        <v>0.19708269755237903</v>
+        <v>0.25205806517736146</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
     </row>
     <row r="20" spans="2:7" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -12605,11 +12688,11 @@
       </c>
       <c r="D21" s="14">
         <f>SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>0</v>
+        <v>118940185</v>
       </c>
       <c r="E21" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>51296036.469999999</v>
+        <v>56102256.469999999</v>
       </c>
       <c r="F21" s="14">
         <f>SUMIFS(รายการรายรับ!I6:I204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
@@ -12617,7 +12700,7 @@
       </c>
       <c r="G21" s="14">
         <f>SUMIFS(รายการรายรับ!J6:J204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>0</v>
+        <v>62837928.530000001</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -12677,11 +12760,11 @@
       </c>
       <c r="D24" s="14">
         <f>SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B24,รายการรายรับ!E6:E204,C24)</f>
-        <v>3572376.17</v>
+        <v>4627281.4000000004</v>
       </c>
       <c r="E24" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B24,รายการรายรับ!E6:E204,C24)</f>
-        <v>3572376.17</v>
+        <v>4627281.4000000004</v>
       </c>
       <c r="F24" s="14">
         <f>SUMIFS(รายการรายรับ!I6:I204,รายการรายรับ!D6:D204,B24,รายการรายรับ!E6:E204,C24)</f>
@@ -12885,13 +12968,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
@@ -12923,11 +13006,11 @@
       </c>
       <c r="E36" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B36,รายการค่าใช้จ่าย!E6:E205,C36)</f>
-        <v>282300</v>
+        <v>479951</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" ref="F36:F74" si="0">IF(D36=0,0,E36/D36)</f>
-        <v>5.6460000000000003E-2</v>
+        <v>9.5990199999999998E-2</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
@@ -12963,11 +13046,11 @@
       </c>
       <c r="E38" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B38,รายการค่าใช้จ่าย!E6:E205,C38)</f>
-        <v>4970063.97</v>
+        <v>5678864.9699999997</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" si="0"/>
-        <v>0.35694738289834671</v>
+        <v>0.4078530982921329</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
@@ -12983,11 +13066,11 @@
       </c>
       <c r="E39" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B39,รายการค่าใช้จ่าย!E6:E205,C39)</f>
-        <v>2223530.96</v>
+        <v>2545706.11</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" si="0"/>
-        <v>0.61954052939537474</v>
+        <v>0.70930791585399833</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
@@ -13003,11 +13086,11 @@
       </c>
       <c r="E40" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B40,รายการค่าใช้จ่าย!E6:E205,C40)</f>
-        <v>2750721.94</v>
+        <v>3102621.94</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" si="0"/>
-        <v>0.7077086394977874</v>
+        <v>0.7982458423381702</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
@@ -13023,11 +13106,11 @@
       </c>
       <c r="E41" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B41,รายการค่าใช้จ่าย!E6:E205,C41)</f>
-        <v>899200</v>
+        <v>1013800</v>
       </c>
       <c r="F41" s="15">
         <f t="shared" si="0"/>
-        <v>0.63449054473609934</v>
+        <v>0.71535421958791989</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
@@ -13043,11 +13126,11 @@
       </c>
       <c r="E42" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B42,รายการค่าใช้จ่าย!E6:E205,C42)</f>
-        <v>10415453.76</v>
+        <v>13033139.629999999</v>
       </c>
       <c r="F42" s="15">
         <f t="shared" si="0"/>
-        <v>0.29456635047767726</v>
+        <v>0.36859885940054182</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
@@ -13063,11 +13146,11 @@
       </c>
       <c r="E43" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B43,รายการค่าใช้จ่าย!E6:E205,C43)</f>
-        <v>266395.61</v>
+        <v>378013.45999999996</v>
       </c>
       <c r="F43" s="15">
         <f t="shared" si="0"/>
-        <v>7.8955426793123881E-2</v>
+        <v>0.11203718435091878</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
@@ -13083,11 +13166,11 @@
       </c>
       <c r="E44" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B44,รายการค่าใช้จ่าย!E6:E205,C44)</f>
-        <v>7274659.4000000004</v>
+        <v>10270068.060000001</v>
       </c>
       <c r="F44" s="15">
         <f t="shared" si="0"/>
-        <v>0.21611552202170253</v>
+        <v>0.30510309802068725</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -13383,11 +13466,11 @@
       </c>
       <c r="E59" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B59,รายการค่าใช้จ่าย!E6:E205,C59)</f>
-        <v>328849.34999999998</v>
+        <v>455424.65</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="0"/>
-        <v>0.1516832795202952</v>
+        <v>0.21006672047970482</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
@@ -13403,11 +13486,11 @@
       </c>
       <c r="E60" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B60,รายการค่าใช้จ่าย!E6:E205,C60)</f>
-        <v>4106698.88</v>
+        <v>5824865.4199999999</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="0"/>
-        <v>8.2963613737373737E-2</v>
+        <v>0.11767404888888888</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
@@ -13683,21 +13766,21 @@
       </c>
       <c r="E74" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B74,รายการค่าใช้จ่าย!E6:E205,C74)</f>
-        <v>606970</v>
+        <v>1054302.77</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="0"/>
-        <v>4.046466666666667E-2</v>
+        <v>7.0286851333333331E-2</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="42" t="s">
+      <c r="B76" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
@@ -13722,19 +13805,19 @@
       </c>
       <c r="C78" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B78)</f>
-        <v>55368412.640000001</v>
+        <v>61229537.869999997</v>
       </c>
       <c r="D78" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B78)</f>
-        <v>29773988.140000001</v>
+        <v>37193827.670000002</v>
       </c>
       <c r="E78" s="14">
         <f>C78-D78</f>
-        <v>25594424.5</v>
+        <v>24035710.199999996</v>
       </c>
       <c r="F78" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B78)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B78),0)</f>
-        <v>8.068402440841421</v>
+        <v>0.48266404499152127</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
@@ -13743,19 +13826,19 @@
       </c>
       <c r="C79" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B79)</f>
-        <v>9778280.75</v>
+        <v>11854110.75</v>
       </c>
       <c r="D79" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B79)</f>
-        <v>4435548.2299999995</v>
+        <v>6280290.0700000003</v>
       </c>
       <c r="E79" s="14">
         <f>C79-D79</f>
-        <v>5342732.5200000005</v>
+        <v>5573820.6799999997</v>
       </c>
       <c r="F79" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B79)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B79),0)</f>
-        <v>0.17142848439691444</v>
+        <v>0.20782101595371669</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
@@ -13768,11 +13851,11 @@
       </c>
       <c r="D80" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B80)</f>
-        <v>606970</v>
+        <v>1054302.77</v>
       </c>
       <c r="E80" s="14">
         <f>C80-D80</f>
-        <v>1505030</v>
+        <v>1057697.23</v>
       </c>
       <c r="F80" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B80)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B80),0)</f>
@@ -13780,14 +13863,14 @@
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="42" t="s">
+      <c r="B82" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="C82" s="42"/>
-      <c r="D82" s="42"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="42"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
@@ -13816,23 +13899,23 @@
       </c>
       <c r="C84" s="29">
         <f>เงินสะสมรายเดือน!D7</f>
-        <v>7000000</v>
+        <v>6975741.9900000002</v>
       </c>
       <c r="D84" s="29">
         <f>เงินสะสมรายเดือน!E7</f>
-        <v>13000000</v>
+        <v>13400251.43</v>
       </c>
       <c r="E84" s="29">
         <f>เงินสะสมรายเดือน!F7</f>
-        <v>144000000</v>
+        <v>144393405.75</v>
       </c>
       <c r="F84" s="29">
         <f>เงินสะสมรายเดือน!G7</f>
-        <v>28000000</v>
+        <v>27674990.490000002</v>
       </c>
       <c r="G84" s="29">
         <f>เงินสะสมรายเดือน!I7</f>
-        <v>172000000</v>
+        <v>172068396.24000001</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.25">
@@ -13842,23 +13925,23 @@
       </c>
       <c r="C85" s="29">
         <f>เงินสะสมรายเดือน!D8</f>
-        <v>1000000</v>
+        <v>6865514.4200000009</v>
       </c>
       <c r="D85" s="29">
         <f>เงินสะสมรายเดือน!E8</f>
-        <v>26000000</v>
+        <v>17135897.079999998</v>
       </c>
       <c r="E85" s="29">
         <f>เงินสะสมรายเดือน!F8</f>
-        <v>134000000</v>
+        <v>134277439.19999999</v>
       </c>
       <c r="F85" s="29">
         <f>เงินสะสมรายเดือน!G8</f>
-        <v>29000000</v>
+        <v>27520574.380000003</v>
       </c>
       <c r="G85" s="29">
         <f>เงินสะสมรายเดือน!I8</f>
-        <v>163000000</v>
+        <v>161798013.57999998</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.25">
@@ -13868,23 +13951,23 @@
       </c>
       <c r="C86" s="29">
         <f>เงินสะสมรายเดือน!D9</f>
-        <v>6000000</v>
+        <v>5731449.7199999997</v>
       </c>
       <c r="D86" s="29">
         <f>เงินสะสมรายเดือน!E9</f>
-        <v>12000000</v>
+        <v>12260580.720000001</v>
       </c>
       <c r="E86" s="29">
         <f>เงินสะสมรายเดือน!F9</f>
-        <v>128000000</v>
+        <v>125158082.45999999</v>
       </c>
       <c r="F86" s="29">
         <f>เงินสะสมรายเดือน!G9</f>
-        <v>29000000</v>
+        <v>30110800.120000001</v>
       </c>
       <c r="G86" s="29">
         <f>เงินสะสมรายเดือน!I9</f>
-        <v>157000000</v>
+        <v>155268882.57999998</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.25">
@@ -13894,23 +13977,23 @@
       </c>
       <c r="C87" s="29">
         <f>เงินสะสมรายเดือน!D10</f>
-        <v>5000000</v>
+        <v>14499881.639999999</v>
       </c>
       <c r="D87" s="29">
         <f>เงินสะสมรายเดือน!E10</f>
-        <v>8000000</v>
+        <v>15364980.280000001</v>
       </c>
       <c r="E87" s="29">
         <f>เงินสะสมรายเดือน!F10</f>
-        <v>124000000</v>
+        <v>124944320.27</v>
       </c>
       <c r="F87" s="29">
         <f>เงินสะสมรายเดือน!G10</f>
-        <v>30000000</v>
+        <v>29459463.669999998</v>
       </c>
       <c r="G87" s="29">
         <f>เงินสะสมรายเดือน!I10</f>
-        <v>154000000</v>
+        <v>154403783.94</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.25">
@@ -13920,23 +14003,23 @@
       </c>
       <c r="C88" s="29">
         <f>เงินสะสมรายเดือน!D11</f>
-        <v>1000000</v>
+        <v>4235099.5600000005</v>
       </c>
       <c r="D88" s="29">
         <f>เงินสะสมรายเดือน!E11</f>
-        <v>3000000</v>
+        <v>9296265.4499999993</v>
       </c>
       <c r="E88" s="29">
         <f>เงินสะสมรายเดือน!F11</f>
-        <v>123000000</v>
+        <v>119987619.17</v>
       </c>
       <c r="F88" s="29">
         <f>เงินสะสมรายเดือน!G11</f>
-        <v>29000000</v>
+        <v>29354998.879999995</v>
       </c>
       <c r="G88" s="29">
         <f>เงินสะสมรายเดือน!I11</f>
-        <v>152000000</v>
+        <v>149342618.05000001</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.25">
@@ -13946,23 +14029,23 @@
       </c>
       <c r="C89" s="29">
         <f>เงินสะสมรายเดือน!D12</f>
-        <v>22000000</v>
+        <v>25255972.079999998</v>
       </c>
       <c r="D89" s="29">
         <f>เงินสะสมรายเดือน!E12</f>
-        <v>9000000</v>
+        <v>10838931.229999999</v>
       </c>
       <c r="E89" s="29">
         <f>เงินสะสมรายเดือน!F12</f>
-        <v>136000000</v>
+        <v>134589258.44</v>
       </c>
       <c r="F89" s="29">
         <f>เงินสะสมรายเดือน!G12</f>
-        <v>29000000</v>
+        <v>29170400.459999993</v>
       </c>
       <c r="G89" s="29">
         <f>เงินสะสมรายเดือน!I12</f>
-        <v>165000000</v>
+        <v>163759658.89999998</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.25">
@@ -13972,23 +14055,23 @@
       </c>
       <c r="C90" s="29">
         <f>เงินสะสมรายเดือน!D13</f>
-        <v>19000000</v>
+        <v>21050413.659999996</v>
       </c>
       <c r="D90" s="29">
         <f>เงินสะสมรายเดือน!E13</f>
-        <v>3000000</v>
+        <v>5892404.5199999996</v>
       </c>
       <c r="E90" s="29">
         <f>เงินสะสมรายเดือน!F13</f>
-        <v>152000000</v>
+        <v>149087761.18000001</v>
       </c>
       <c r="F90" s="29">
         <f>เงินสะสมรายเดือน!G13</f>
-        <v>28000000</v>
+        <v>29829906.859999992</v>
       </c>
       <c r="G90" s="29">
         <f>เงินสะสมรายเดือน!I13</f>
-        <v>180000000</v>
+        <v>178917668.03999999</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.25">
@@ -13998,23 +14081,23 @@
       </c>
       <c r="C91" s="29">
         <f>เงินสะสมรายเดือน!D14</f>
-        <v>3000000</v>
+        <v>15109798.050000001</v>
       </c>
       <c r="D91" s="29">
         <f>เงินสะสมรายเดือน!E14</f>
-        <v>10000000</v>
+        <v>15983680.49</v>
       </c>
       <c r="E91" s="29">
         <f>เงินสะสมรายเดือน!F14</f>
-        <v>140000000</v>
+        <v>149154182.69</v>
       </c>
       <c r="F91" s="29">
         <f>เงินสะสมรายเดือน!G14</f>
-        <v>33000000</v>
+        <v>28889602.909999989</v>
       </c>
       <c r="G91" s="29">
         <f>เงินสะสมรายเดือน!I14</f>
-        <v>173000000</v>
+        <v>178043785.59999999</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.25">

--- a/Financial_Dashboard_Template_Full.xlsx
+++ b/Financial_Dashboard_Template_Full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365cmu-my.sharepoint.com/personal/kanyaphak_su_cmu_ac_th/Documents/KANYAPHAK/07 นำเสนอข้อมูล กบว/00-นำเสนอข้อมูล/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A552E6-B272-4ACB-8103-E00096C2D66A}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{063B9F43-A81A-4C66-88DB-773E2D705F4B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,12 +852,13 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -866,7 +867,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -951,10 +951,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1167,322 +1163,307 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B19:H19"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C28:H28"/>
@@ -1492,6 +1473,21 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1510,13 +1506,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1540,7 +1536,7 @@
       </c>
       <c r="C5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1683,12 +1679,12 @@
       <c r="D27" s="6"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1718,32 +1714,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
     </row>
     <row r="5" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -6844,13 +6840,13 @@
       <c r="L204" s="16"/>
     </row>
     <row r="205" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="43" t="s">
+      <c r="B205" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="C205" s="43"/>
-      <c r="D205" s="43"/>
-      <c r="E205" s="43"/>
-      <c r="F205" s="43"/>
+      <c r="C205" s="44"/>
+      <c r="D205" s="44"/>
+      <c r="E205" s="44"/>
+      <c r="F205" s="44"/>
       <c r="G205" s="18">
         <f>SUM(G6:G204)</f>
         <v>198897466.40000001</v>
@@ -6923,30 +6919,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
     </row>
     <row r="5" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -11919,13 +11915,13 @@
       <c r="K205" s="16"/>
     </row>
     <row r="206" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="43" t="s">
+      <c r="B206" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="C206" s="43"/>
-      <c r="D206" s="43"/>
-      <c r="E206" s="43"/>
-      <c r="F206" s="43"/>
+      <c r="C206" s="44"/>
+      <c r="D206" s="44"/>
+      <c r="E206" s="44"/>
+      <c r="F206" s="44"/>
       <c r="G206" s="18">
         <f>SUM(G6:G205)</f>
         <v>176659376</v>
@@ -11991,28 +11987,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -12056,16 +12052,16 @@
       <c r="C7" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="38">
         <v>6975741.9900000002</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="38">
         <v>13400251.43</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="38">
         <v>144393405.75</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="38">
         <v>27674990.490000002</v>
       </c>
       <c r="H7" s="14">
@@ -12084,34 +12080,34 @@
       <c r="C8" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="38">
         <v>6865514.4200000009</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="38">
         <v>17135897.079999998</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="38">
         <v>134277439.19999999</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="38">
         <v>27520574.380000003</v>
       </c>
       <c r="H8" s="14">
-        <f t="shared" ref="H7:H19" si="0">D8-E8</f>
+        <f t="shared" ref="H8:H19" si="0">D8-E8</f>
         <v>-10270382.659999996</v>
       </c>
       <c r="I8" s="14">
-        <f t="shared" ref="I7:I19" si="1">F8+G8</f>
+        <f t="shared" ref="I8:I19" si="1">F8+G8</f>
         <v>161798013.57999998</v>
       </c>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="7">
@@ -12120,16 +12116,16 @@
       <c r="C9" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="38">
         <v>5731449.7199999997</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="38">
         <v>12260580.720000001</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="38">
         <v>125158082.45999999</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="38">
         <v>30110800.120000001</v>
       </c>
       <c r="H9" s="14">
@@ -12140,14 +12136,14 @@
         <f t="shared" si="1"/>
         <v>155268882.57999998</v>
       </c>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
@@ -12156,16 +12152,16 @@
       <c r="C10" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="38">
         <v>14499881.639999999</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="38">
         <v>15364980.280000001</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="38">
         <v>124944320.27</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="38">
         <v>29459463.669999998</v>
       </c>
       <c r="H10" s="14">
@@ -12176,14 +12172,14 @@
         <f t="shared" si="1"/>
         <v>154403783.94</v>
       </c>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="7">
@@ -12192,16 +12188,16 @@
       <c r="C11" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="38">
         <v>4235099.5600000005</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="38">
         <v>9296265.4499999993</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="38">
         <v>119987619.17</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="38">
         <v>29354998.879999995</v>
       </c>
       <c r="H11" s="14">
@@ -12212,14 +12208,14 @@
         <f t="shared" si="1"/>
         <v>149342618.05000001</v>
       </c>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="7">
@@ -12228,16 +12224,16 @@
       <c r="C12" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="38">
         <v>25255972.079999998</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="38">
         <v>10838931.229999999</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="38">
         <v>134589258.44</v>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="38">
         <v>29170400.459999993</v>
       </c>
       <c r="H12" s="14">
@@ -12256,16 +12252,16 @@
       <c r="C13" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="38">
         <v>21050413.659999996</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="38">
         <v>5892404.5199999996</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="38">
         <v>149087761.18000001</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="38">
         <v>29829906.859999992</v>
       </c>
       <c r="H13" s="14">
@@ -12284,16 +12280,16 @@
       <c r="C14" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="38">
         <v>15109798.050000001</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="38">
         <v>15983680.49</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="38">
         <v>149154182.69</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="38">
         <v>28889602.909999989</v>
       </c>
       <c r="H14" s="14">
@@ -12313,24 +12309,25 @@
         <v>123</v>
       </c>
       <c r="D15" s="25">
-        <v>4000000</v>
+        <f>3900000+2273595.28</f>
+        <v>6173595.2799999993</v>
       </c>
       <c r="E15" s="21">
-        <v>10000000</v>
+        <v>15000000</v>
       </c>
       <c r="F15" s="26">
-        <v>134000000</v>
+        <v>133665859.38</v>
       </c>
       <c r="G15" s="26">
-        <v>33000000</v>
+        <v>32577549.809999999</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" si="0"/>
-        <v>-6000000</v>
+        <v>-8826404.7200000007</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" si="1"/>
-        <v>167000000</v>
+        <v>166243409.19</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
@@ -12341,24 +12338,24 @@
         <v>124</v>
       </c>
       <c r="D16" s="25">
-        <v>28000000</v>
+        <v>20000000</v>
       </c>
       <c r="E16" s="21">
-        <v>10000000</v>
+        <v>12000000</v>
       </c>
       <c r="F16" s="26">
-        <v>129000000</v>
+        <v>128583896.81999999</v>
       </c>
       <c r="G16" s="26">
-        <v>42000000</v>
+        <v>42035393.549999997</v>
       </c>
       <c r="H16" s="14">
         <f t="shared" si="0"/>
-        <v>18000000</v>
+        <v>8000000</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="1"/>
-        <v>171000000</v>
+        <v>170619290.37</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -12369,24 +12366,24 @@
         <v>125</v>
       </c>
       <c r="D17" s="25">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="E17" s="21">
         <v>10000000</v>
       </c>
       <c r="F17" s="26">
-        <v>118000000</v>
+        <v>118259577.73</v>
       </c>
       <c r="G17" s="26">
-        <v>43000000</v>
+        <v>43002048.759999998</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" si="0"/>
-        <v>-5000000</v>
+        <v>-6000000</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" si="1"/>
-        <v>161000000</v>
+        <v>161261626.49000001</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -12397,54 +12394,55 @@
         <v>126</v>
       </c>
       <c r="D18" s="25">
-        <v>57000000</v>
+        <v>54000000</v>
       </c>
       <c r="E18" s="21">
-        <v>10000000</v>
+        <f>10000000+14486384.8</f>
+        <v>24486384.800000001</v>
       </c>
       <c r="F18" s="26">
-        <v>150000000</v>
+        <v>149951797.47</v>
       </c>
       <c r="G18" s="26">
-        <v>42000000</v>
+        <v>41891871.549999997</v>
       </c>
       <c r="H18" s="14">
         <f t="shared" si="0"/>
-        <v>47000000</v>
+        <v>29513615.199999999</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" si="1"/>
-        <v>192000000</v>
+        <v>191843669.01999998</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="44"/>
+      <c r="C19" s="45"/>
       <c r="D19" s="18">
         <f>SUM(D7:D18)</f>
-        <v>193723871.12</v>
+        <v>183897466.39999998</v>
       </c>
       <c r="E19" s="18">
         <f>SUM(E7:E18)</f>
-        <v>140172991.19999999</v>
+        <v>161659376</v>
       </c>
       <c r="F19" s="18">
         <f>F18</f>
-        <v>150000000</v>
+        <v>149951797.47</v>
       </c>
       <c r="G19" s="18">
         <f>G18</f>
-        <v>42000000</v>
+        <v>41891871.549999997</v>
       </c>
       <c r="H19" s="18">
         <f t="shared" si="0"/>
-        <v>53550879.920000017</v>
+        <v>22238090.399999976</v>
       </c>
       <c r="I19" s="18">
         <f t="shared" si="1"/>
-        <v>192000000</v>
+        <v>191843669.01999998</v>
       </c>
     </row>
   </sheetData>
@@ -12496,21 +12494,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -12584,11 +12582,11 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -12650,14 +12648,14 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="2:7" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -12968,13 +12966,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
@@ -13774,13 +13772,13 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="45" t="s">
+      <c r="B76" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
@@ -13863,14 +13861,14 @@
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="45" t="s">
+      <c r="B82" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="45"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="46"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
@@ -14107,23 +14105,23 @@
       </c>
       <c r="C92" s="29">
         <f>เงินสะสมรายเดือน!D15</f>
-        <v>4000000</v>
+        <v>6173595.2799999993</v>
       </c>
       <c r="D92" s="29">
         <f>เงินสะสมรายเดือน!E15</f>
-        <v>10000000</v>
+        <v>15000000</v>
       </c>
       <c r="E92" s="29">
         <f>เงินสะสมรายเดือน!F15</f>
-        <v>134000000</v>
+        <v>133665859.38</v>
       </c>
       <c r="F92" s="29">
         <f>เงินสะสมรายเดือน!G15</f>
-        <v>33000000</v>
+        <v>32577549.809999999</v>
       </c>
       <c r="G92" s="29">
         <f>เงินสะสมรายเดือน!I15</f>
-        <v>167000000</v>
+        <v>166243409.19</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.25">
@@ -14133,23 +14131,23 @@
       </c>
       <c r="C93" s="29">
         <f>เงินสะสมรายเดือน!D16</f>
-        <v>28000000</v>
+        <v>20000000</v>
       </c>
       <c r="D93" s="29">
         <f>เงินสะสมรายเดือน!E16</f>
-        <v>10000000</v>
+        <v>12000000</v>
       </c>
       <c r="E93" s="29">
         <f>เงินสะสมรายเดือน!F16</f>
-        <v>129000000</v>
+        <v>128583896.81999999</v>
       </c>
       <c r="F93" s="29">
         <f>เงินสะสมรายเดือน!G16</f>
-        <v>42000000</v>
+        <v>42035393.549999997</v>
       </c>
       <c r="G93" s="29">
         <f>เงินสะสมรายเดือน!I16</f>
-        <v>171000000</v>
+        <v>170619290.37</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.25">
@@ -14159,7 +14157,7 @@
       </c>
       <c r="C94" s="29">
         <f>เงินสะสมรายเดือน!D17</f>
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="D94" s="29">
         <f>เงินสะสมรายเดือน!E17</f>
@@ -14167,15 +14165,15 @@
       </c>
       <c r="E94" s="29">
         <f>เงินสะสมรายเดือน!F17</f>
-        <v>118000000</v>
+        <v>118259577.73</v>
       </c>
       <c r="F94" s="29">
         <f>เงินสะสมรายเดือน!G17</f>
-        <v>43000000</v>
+        <v>43002048.759999998</v>
       </c>
       <c r="G94" s="29">
         <f>เงินสะสมรายเดือน!I17</f>
-        <v>161000000</v>
+        <v>161261626.49000001</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.25">
@@ -14185,23 +14183,23 @@
       </c>
       <c r="C95" s="29">
         <f>เงินสะสมรายเดือน!D18</f>
-        <v>57000000</v>
+        <v>54000000</v>
       </c>
       <c r="D95" s="29">
         <f>เงินสะสมรายเดือน!E18</f>
-        <v>10000000</v>
+        <v>24486384.800000001</v>
       </c>
       <c r="E95" s="29">
         <f>เงินสะสมรายเดือน!F18</f>
-        <v>150000000</v>
+        <v>149951797.47</v>
       </c>
       <c r="F95" s="29">
         <f>เงินสะสมรายเดือน!G18</f>
-        <v>42000000</v>
+        <v>41891871.549999997</v>
       </c>
       <c r="G95" s="29">
         <f>เงินสะสมรายเดือน!I18</f>
-        <v>192000000</v>
+        <v>191843669.01999998</v>
       </c>
     </row>
   </sheetData>

--- a/Financial_Dashboard_Template_Full.xlsx
+++ b/Financial_Dashboard_Template_Full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365cmu-my.sharepoint.com/personal/kanyaphak_su_cmu_ac_th/Documents/KANYAPHAK/07 นำเสนอข้อมูล กบว/00-นำเสนอข้อมูล/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{063B9F43-A81A-4C66-88DB-773E2D705F4B}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D42CCFE2-4DA1-41D8-826A-CFEF06979621}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -757,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -853,12 +853,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -867,6 +867,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1163,307 +1166,322 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
     </row>
     <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="B19:H19"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C28:H28"/>
@@ -1473,21 +1491,6 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C7:H7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1506,13 +1509,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1536,7 +1539,7 @@
       </c>
       <c r="C5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1714,18 +1717,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="43" t="s">
@@ -1798,17 +1801,17 @@
         <v>118940185</v>
       </c>
       <c r="H6" s="12">
-        <f>51296036.47+4806220</f>
-        <v>56102256.469999999</v>
+        <f>51296036.47+4806220+1007300</f>
+        <v>57109556.469999999</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="14">
         <f t="shared" ref="J6:J36" si="1">IF(G6="","",IFERROR(G6-H6-I6,0))</f>
-        <v>62837928.530000001</v>
+        <v>61830628.530000001</v>
       </c>
       <c r="K6" s="15">
         <f t="shared" ref="K6:K36" si="2">IF(OR(G6="",G6=0),"",H6/G6)</f>
-        <v>0.4716846242504163</v>
+        <v>0.48015358703200267</v>
       </c>
       <c r="L6" s="16"/>
     </row>
@@ -1975,19 +1978,19 @@
         <v>51300000</v>
       </c>
       <c r="H11" s="35">
-        <v>10849662.1</v>
+        <v>13962422.1</v>
       </c>
       <c r="I11" s="36">
-        <f>20946148.07-10849662.1</f>
-        <v>10096485.970000001</v>
+        <f>22968748.07-H11</f>
+        <v>9006325.9700000007</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v>30353851.93</v>
+        <v>28331251.93</v>
       </c>
       <c r="K11" s="15">
         <f t="shared" si="2"/>
-        <v>0.21149438791423</v>
+        <v>0.27217197076023392</v>
       </c>
       <c r="L11" s="16"/>
     </row>
@@ -2047,8 +2050,9 @@
       <c r="G13" s="32">
         <v>15000000</v>
       </c>
-      <c r="H13" s="33">
-        <v>2112000</v>
+      <c r="H13" s="47">
+        <f>2112000+200000</f>
+        <v>2312000</v>
       </c>
       <c r="I13" s="36">
         <f>4080000-2112000</f>
@@ -2056,11 +2060,11 @@
       </c>
       <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v>10920000</v>
+        <v>10720000</v>
       </c>
       <c r="K13" s="15">
         <f t="shared" si="2"/>
-        <v>0.14080000000000001</v>
+        <v>0.15413333333333334</v>
       </c>
       <c r="L13" s="16"/>
     </row>
@@ -6853,19 +6857,19 @@
       </c>
       <c r="H205" s="18">
         <f>SUM(H6:H204)</f>
-        <v>75195648.61999999</v>
+        <v>79515708.61999999</v>
       </c>
       <c r="I205" s="18">
         <f>SUM(I6:I204)</f>
-        <v>12064485.970000001</v>
+        <v>10974325.970000001</v>
       </c>
       <c r="J205" s="18">
         <f>SUM(J6:J204)</f>
-        <v>111637331.81</v>
+        <v>108407431.81</v>
       </c>
       <c r="K205" s="19">
         <f>IF(G205=0,0,H205/G205)</f>
-        <v>0.37806237545919785</v>
+        <v>0.39978241080299648</v>
       </c>
       <c r="L205" s="20"/>
     </row>
@@ -6919,17 +6923,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="43" t="s">
@@ -6998,16 +7002,15 @@
         <v>5000000</v>
       </c>
       <c r="H6" s="22">
-        <f>282300+197651</f>
-        <v>479951</v>
+        <v>536651</v>
       </c>
       <c r="I6" s="14">
         <f>IF(G6="","",G6-H6)</f>
-        <v>4520049</v>
+        <v>4463349</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" ref="J6:J37" si="1">IF(OR(G6="",G6=0),"",H6/G6)</f>
-        <v>9.5990199999999998E-2</v>
+        <v>0.1073302</v>
       </c>
       <c r="K6" s="16"/>
     </row>
@@ -7033,15 +7036,15 @@
         <v>2281000</v>
       </c>
       <c r="H7" s="22">
-        <v>691662.5</v>
+        <v>1633133.5</v>
       </c>
       <c r="I7" s="14">
         <f t="shared" ref="I7:I37" si="2">IF(G7="","",G7-H7)</f>
-        <v>1589337.5</v>
+        <v>647866.5</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>0.30322775098640947</v>
+        <v>0.71597259973695748</v>
       </c>
       <c r="K7" s="16"/>
     </row>
@@ -7067,16 +7070,15 @@
         <v>13923800</v>
       </c>
       <c r="H8" s="22">
-        <f>4970063.97+708801</f>
-        <v>5678864.9699999997</v>
+        <v>6386315.9700000007</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="2"/>
-        <v>8244935.0300000003</v>
+        <v>7537484.0299999993</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>0.4078530982921329</v>
+        <v>0.45866185739525134</v>
       </c>
       <c r="K8" s="16"/>
     </row>
@@ -7102,16 +7104,15 @@
         <v>3589000</v>
       </c>
       <c r="H9" s="22">
-        <f>2223530.96+322175.15</f>
-        <v>2545706.11</v>
+        <v>2871989.07</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" si="2"/>
-        <v>1043293.8900000001</v>
+        <v>717010.93000000017</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>0.70930791585399833</v>
+        <v>0.80021985789913619</v>
       </c>
       <c r="K9" s="16"/>
     </row>
@@ -7137,16 +7138,15 @@
         <v>3886800</v>
       </c>
       <c r="H10" s="22">
-        <f>2750721.94+351900</f>
-        <v>3102621.94</v>
+        <v>3454521.94</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" si="2"/>
-        <v>784178.06</v>
+        <v>432278.06000000006</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>0.7982458423381702</v>
+        <v>0.888783045178553</v>
       </c>
       <c r="K10" s="16"/>
     </row>
@@ -7172,16 +7172,15 @@
         <v>1417200</v>
       </c>
       <c r="H11" s="22">
-        <f>899200+114600</f>
-        <v>1013800</v>
+        <v>1128400</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" si="2"/>
-        <v>403400</v>
+        <v>288800</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>0.71535421958791989</v>
+        <v>0.79621789443974034</v>
       </c>
       <c r="K11" s="16"/>
     </row>
@@ -7207,16 +7206,15 @@
         <v>35358600</v>
       </c>
       <c r="H12" s="22">
-        <f>10415453.76+2617685.87</f>
-        <v>13033139.629999999</v>
+        <v>17125151.799999997</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" si="2"/>
-        <v>22325460.370000001</v>
+        <v>18233448.200000003</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>0.36859885940054182</v>
+        <v>0.48432776750210688</v>
       </c>
       <c r="K12" s="16"/>
     </row>
@@ -7242,16 +7240,15 @@
         <v>3374000</v>
       </c>
       <c r="H13" s="22">
-        <f>266395.61+111617.85</f>
-        <v>378013.45999999996</v>
+        <v>555254.03999999992</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" si="2"/>
-        <v>2995986.54</v>
+        <v>2818745.96</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>0.11203718435091878</v>
+        <v>0.16456847658565499</v>
       </c>
       <c r="K13" s="16"/>
     </row>
@@ -7277,16 +7274,15 @@
         <v>33660976</v>
       </c>
       <c r="H14" s="22">
-        <f>7274659.4+2995408.66</f>
-        <v>10270068.060000001</v>
+        <v>12303669.59</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="2"/>
-        <v>23390907.939999998</v>
+        <v>21357306.41</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>0.30510309802068725</v>
+        <v>0.36551731565953405</v>
       </c>
       <c r="K14" s="16"/>
     </row>
@@ -7346,15 +7342,15 @@
         <v>2168000</v>
       </c>
       <c r="H16" s="37">
-        <v>455424.65</v>
+        <v>501060.05</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="2"/>
-        <v>1712575.35</v>
+        <v>1666939.95</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>0.21006672047970482</v>
+        <v>0.23111625922509224</v>
       </c>
       <c r="K16" s="16"/>
     </row>
@@ -7380,15 +7376,15 @@
         <v>49500000</v>
       </c>
       <c r="H17" s="37">
-        <v>5824865.4199999999</v>
+        <v>8723875.2599999998</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" si="2"/>
-        <v>43675134.579999998</v>
+        <v>40776124.740000002</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>0.11767404888888888</v>
+        <v>0.17623990424242425</v>
       </c>
       <c r="K17" s="16"/>
     </row>
@@ -7414,15 +7410,15 @@
         <v>15000000</v>
       </c>
       <c r="H18" s="37">
-        <v>1054302.77</v>
+        <v>1031172.77</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" si="2"/>
-        <v>13945697.23</v>
+        <v>13968827.23</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>7.0286851333333331E-2</v>
+        <v>6.8744851333333329E-2</v>
       </c>
       <c r="K18" s="16"/>
     </row>
@@ -11928,15 +11924,15 @@
       </c>
       <c r="H206" s="18">
         <f>SUM(H6:H205)</f>
-        <v>44528420.510000005</v>
+        <v>56251194.989999995</v>
       </c>
       <c r="I206" s="18">
         <f>SUM(I6:I205)</f>
-        <v>132130955.48999999</v>
+        <v>120408181.01000001</v>
       </c>
       <c r="J206" s="19">
         <f>IF(G206=0,0,H206/G206)</f>
-        <v>0.25205806517736146</v>
+        <v>0.31841613088229176</v>
       </c>
       <c r="K206" s="20"/>
     </row>
@@ -11987,16 +11983,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" s="43" t="s">
@@ -12494,14 +12490,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="46" t="s">
@@ -12539,7 +12535,7 @@
       </c>
       <c r="C7" s="14">
         <f>SUM(รายการรายรับ!H6:H204)</f>
-        <v>75195648.61999999</v>
+        <v>79515708.61999999</v>
       </c>
       <c r="D7" s="28" t="s">
         <v>134</v>
@@ -12551,7 +12547,7 @@
       </c>
       <c r="C8" s="14">
         <f>SUM(รายการรายรับ!I6:I204)</f>
-        <v>12064485.970000001</v>
+        <v>10974325.970000001</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>134</v>
@@ -12563,7 +12559,7 @@
       </c>
       <c r="C9" s="14">
         <f>SUM(รายการรายรับ!J6:J204)</f>
-        <v>111637331.81</v>
+        <v>108407431.81</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>134</v>
@@ -12575,7 +12571,7 @@
       </c>
       <c r="C10" s="15">
         <f>IF(SUM(รายการรายรับ!G6:G204)=0,0,SUM(รายการรายรับ!H6:H204)/SUM(รายการรายรับ!G6:G204))</f>
-        <v>0.37806237545919785</v>
+        <v>0.39978241080299648</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>137</v>
@@ -12617,7 +12613,7 @@
       </c>
       <c r="C15" s="14">
         <f>SUM(รายการค่าใช้จ่าย!H6:H205)</f>
-        <v>44528420.510000005</v>
+        <v>56251194.989999995</v>
       </c>
       <c r="D15" s="28" t="s">
         <v>134</v>
@@ -12629,7 +12625,7 @@
       </c>
       <c r="C16" s="14">
         <f>SUM(รายการค่าใช้จ่าย!G6:G205)-SUM(รายการค่าใช้จ่าย!H6:H205)</f>
-        <v>132130955.48999999</v>
+        <v>120408181.01000001</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>134</v>
@@ -12641,7 +12637,7 @@
       </c>
       <c r="C17" s="15">
         <f>IF(SUM(รายการค่าใช้จ่าย!G6:G205)=0,0,SUM(รายการค่าใช้จ่าย!H6:H205)/SUM(รายการค่าใช้จ่าย!G6:G205))</f>
-        <v>0.25205806517736146</v>
+        <v>0.31841613088229176</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>137</v>
@@ -12690,7 +12686,7 @@
       </c>
       <c r="E21" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>56102256.469999999</v>
+        <v>57109556.469999999</v>
       </c>
       <c r="F21" s="14">
         <f>SUMIFS(รายการรายรับ!I6:I204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
@@ -12698,7 +12694,7 @@
       </c>
       <c r="G21" s="14">
         <f>SUMIFS(รายการรายรับ!J6:J204,รายการรายรับ!D6:D204,B21,รายการรายรับ!E6:E204,C21)</f>
-        <v>62837928.530000001</v>
+        <v>61830628.530000001</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -13004,11 +13000,11 @@
       </c>
       <c r="E36" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B36,รายการค่าใช้จ่าย!E6:E205,C36)</f>
-        <v>479951</v>
+        <v>536651</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" ref="F36:F74" si="0">IF(D36=0,0,E36/D36)</f>
-        <v>9.5990199999999998E-2</v>
+        <v>0.1073302</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
@@ -13024,11 +13020,11 @@
       </c>
       <c r="E37" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B37,รายการค่าใช้จ่าย!E6:E205,C37)</f>
-        <v>691662.5</v>
+        <v>1633133.5</v>
       </c>
       <c r="F37" s="15">
         <f t="shared" si="0"/>
-        <v>0.30322775098640947</v>
+        <v>0.71597259973695748</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
@@ -13044,11 +13040,11 @@
       </c>
       <c r="E38" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B38,รายการค่าใช้จ่าย!E6:E205,C38)</f>
-        <v>5678864.9699999997</v>
+        <v>6386315.9700000007</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" si="0"/>
-        <v>0.4078530982921329</v>
+        <v>0.45866185739525134</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
@@ -13064,11 +13060,11 @@
       </c>
       <c r="E39" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B39,รายการค่าใช้จ่าย!E6:E205,C39)</f>
-        <v>2545706.11</v>
+        <v>2871989.07</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" si="0"/>
-        <v>0.70930791585399833</v>
+        <v>0.80021985789913619</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
@@ -13084,11 +13080,11 @@
       </c>
       <c r="E40" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B40,รายการค่าใช้จ่าย!E6:E205,C40)</f>
-        <v>3102621.94</v>
+        <v>3454521.94</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" si="0"/>
-        <v>0.7982458423381702</v>
+        <v>0.888783045178553</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
@@ -13104,11 +13100,11 @@
       </c>
       <c r="E41" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B41,รายการค่าใช้จ่าย!E6:E205,C41)</f>
-        <v>1013800</v>
+        <v>1128400</v>
       </c>
       <c r="F41" s="15">
         <f t="shared" si="0"/>
-        <v>0.71535421958791989</v>
+        <v>0.79621789443974034</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
@@ -13124,11 +13120,11 @@
       </c>
       <c r="E42" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B42,รายการค่าใช้จ่าย!E6:E205,C42)</f>
-        <v>13033139.629999999</v>
+        <v>17125151.799999997</v>
       </c>
       <c r="F42" s="15">
         <f t="shared" si="0"/>
-        <v>0.36859885940054182</v>
+        <v>0.48432776750210688</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
@@ -13144,11 +13140,11 @@
       </c>
       <c r="E43" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B43,รายการค่าใช้จ่าย!E6:E205,C43)</f>
-        <v>378013.45999999996</v>
+        <v>555254.03999999992</v>
       </c>
       <c r="F43" s="15">
         <f t="shared" si="0"/>
-        <v>0.11203718435091878</v>
+        <v>0.16456847658565499</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
@@ -13164,11 +13160,11 @@
       </c>
       <c r="E44" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B44,รายการค่าใช้จ่าย!E6:E205,C44)</f>
-        <v>10270068.060000001</v>
+        <v>12303669.59</v>
       </c>
       <c r="F44" s="15">
         <f t="shared" si="0"/>
-        <v>0.30510309802068725</v>
+        <v>0.36551731565953405</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -13464,11 +13460,11 @@
       </c>
       <c r="E59" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B59,รายการค่าใช้จ่าย!E6:E205,C59)</f>
-        <v>455424.65</v>
+        <v>501060.05</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="0"/>
-        <v>0.21006672047970482</v>
+        <v>0.23111625922509224</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
@@ -13484,11 +13480,11 @@
       </c>
       <c r="E60" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B60,รายการค่าใช้จ่าย!E6:E205,C60)</f>
-        <v>5824865.4199999999</v>
+        <v>8723875.2599999998</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="0"/>
-        <v>0.11767404888888888</v>
+        <v>0.17623990424242425</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
@@ -13764,11 +13760,11 @@
       </c>
       <c r="E74" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B74,รายการค่าใช้จ่าย!E6:E205,C74)</f>
-        <v>1054302.77</v>
+        <v>1031172.77</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="0"/>
-        <v>7.0286851333333331E-2</v>
+        <v>6.8744851333333329E-2</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
@@ -13803,19 +13799,19 @@
       </c>
       <c r="C78" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B78)</f>
-        <v>61229537.869999997</v>
+        <v>62236837.869999997</v>
       </c>
       <c r="D78" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B78)</f>
-        <v>37193827.670000002</v>
+        <v>45995086.909999996</v>
       </c>
       <c r="E78" s="14">
         <f>C78-D78</f>
-        <v>24035710.199999996</v>
+        <v>16241750.960000001</v>
       </c>
       <c r="F78" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B78)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B78),0)</f>
-        <v>0.48266404499152127</v>
+        <v>0.49060445266783281</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
@@ -13824,19 +13820,19 @@
       </c>
       <c r="C79" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B79)</f>
-        <v>11854110.75</v>
+        <v>14966870.75</v>
       </c>
       <c r="D79" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B79)</f>
-        <v>6280290.0700000003</v>
+        <v>9224935.3100000005</v>
       </c>
       <c r="E79" s="14">
         <f>C79-D79</f>
-        <v>5573820.6799999997</v>
+        <v>5741935.4399999995</v>
       </c>
       <c r="F79" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B79)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B79),0)</f>
-        <v>0.20782101595371669</v>
+        <v>0.26239254470546985</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
@@ -13845,19 +13841,19 @@
       </c>
       <c r="C80" s="14">
         <f>SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B80)</f>
-        <v>2112000</v>
+        <v>2312000</v>
       </c>
       <c r="D80" s="14">
         <f>SUMIFS(รายการค่าใช้จ่าย!H6:H205,รายการค่าใช้จ่าย!D6:D205,B80)</f>
-        <v>1054302.77</v>
+        <v>1031172.77</v>
       </c>
       <c r="E80" s="14">
         <f>C80-D80</f>
-        <v>1057697.23</v>
+        <v>1280827.23</v>
       </c>
       <c r="F80" s="15">
         <f>IFERROR(SUMIFS(รายการรายรับ!H6:H204,รายการรายรับ!D6:D204,B80)/SUMIFS(รายการรายรับ!G6:G204,รายการรายรับ!D6:D204,B80),0)</f>
-        <v>0.14080000000000001</v>
+        <v>0.15413333333333334</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">

--- a/Financial_Dashboard_Template_Full.xlsx
+++ b/Financial_Dashboard_Template_Full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365cmu-my.sharepoint.com/personal/kanyaphak_su_cmu_ac_th/Documents/KANYAPHAK/07 นำเสนอข้อมูล กบว/00-นำเสนอข้อมูล/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D42CCFE2-4DA1-41D8-826A-CFEF06979621}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="11_328A28D6332C55D98B583AA4756567A8E4791857" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DA467C7-8A58-4FEB-99EC-F999D2B89090}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-600" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -757,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -853,6 +853,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -867,7 +870,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1166,304 +1169,304 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1509,13 +1512,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1682,12 +1685,12 @@
       <c r="D27" s="6"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1717,32 +1720,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
     </row>
     <row r="5" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -2050,7 +2053,7 @@
       <c r="G13" s="32">
         <v>15000000</v>
       </c>
-      <c r="H13" s="47">
+      <c r="H13" s="39">
         <f>2112000+200000</f>
         <v>2312000</v>
       </c>
@@ -6844,13 +6847,13 @@
       <c r="L204" s="16"/>
     </row>
     <row r="205" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="44" t="s">
+      <c r="B205" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="C205" s="44"/>
-      <c r="D205" s="44"/>
-      <c r="E205" s="44"/>
-      <c r="F205" s="44"/>
+      <c r="C205" s="45"/>
+      <c r="D205" s="45"/>
+      <c r="E205" s="45"/>
+      <c r="F205" s="45"/>
       <c r="G205" s="18">
         <f>SUM(G6:G204)</f>
         <v>198897466.40000001</v>
@@ -6923,30 +6926,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="5" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -11911,13 +11914,13 @@
       <c r="K205" s="16"/>
     </row>
     <row r="206" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="44" t="s">
+      <c r="B206" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="C206" s="44"/>
-      <c r="D206" s="44"/>
-      <c r="E206" s="44"/>
-      <c r="F206" s="44"/>
+      <c r="C206" s="45"/>
+      <c r="D206" s="45"/>
+      <c r="E206" s="45"/>
+      <c r="F206" s="45"/>
       <c r="G206" s="18">
         <f>SUM(G6:G205)</f>
         <v>176659376</v>
@@ -11983,28 +11986,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -12304,26 +12307,25 @@
       <c r="C15" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="25">
-        <f>3900000+2273595.28</f>
-        <v>6173595.2799999993</v>
-      </c>
-      <c r="E15" s="21">
-        <v>15000000</v>
-      </c>
-      <c r="F15" s="26">
-        <v>133665859.38</v>
-      </c>
-      <c r="G15" s="26">
-        <v>32577549.809999999</v>
+      <c r="D15" s="48">
+        <v>3125534.2</v>
+      </c>
+      <c r="E15" s="48">
+        <v>8259204.6500000004</v>
+      </c>
+      <c r="F15" s="48">
+        <v>143558445.97</v>
+      </c>
+      <c r="G15" s="48">
+        <v>29351669.179999992</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" si="0"/>
-        <v>-8826404.7200000007</v>
+        <v>-5133670.45</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" si="1"/>
-        <v>166243409.19</v>
+        <v>172910115.14999998</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
@@ -12412,17 +12414,17 @@
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="45"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="18">
         <f>SUM(D7:D18)</f>
-        <v>183897466.39999998</v>
+        <v>180849405.31999999</v>
       </c>
       <c r="E19" s="18">
         <f>SUM(E7:E18)</f>
-        <v>161659376</v>
+        <v>154918580.65000001</v>
       </c>
       <c r="F19" s="18">
         <f>F18</f>
@@ -12434,7 +12436,7 @@
       </c>
       <c r="H19" s="18">
         <f t="shared" si="0"/>
-        <v>22238090.399999976</v>
+        <v>25930824.669999987</v>
       </c>
       <c r="I19" s="18">
         <f t="shared" si="1"/>
@@ -12490,21 +12492,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
     </row>
     <row r="5" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -12578,11 +12580,11 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -12644,14 +12646,14 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
     </row>
     <row r="20" spans="2:7" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -12962,13 +12964,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
@@ -13768,13 +13770,13 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="46" t="s">
+      <c r="B76" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="47"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
@@ -13857,14 +13859,14 @@
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="46" t="s">
+      <c r="B82" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="C82" s="46"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
+      <c r="C82" s="47"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="47"/>
+      <c r="G82" s="47"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
@@ -14101,23 +14103,23 @@
       </c>
       <c r="C92" s="29">
         <f>เงินสะสมรายเดือน!D15</f>
-        <v>6173595.2799999993</v>
+        <v>3125534.2</v>
       </c>
       <c r="D92" s="29">
         <f>เงินสะสมรายเดือน!E15</f>
-        <v>15000000</v>
+        <v>8259204.6500000004</v>
       </c>
       <c r="E92" s="29">
         <f>เงินสะสมรายเดือน!F15</f>
-        <v>133665859.38</v>
+        <v>143558445.97</v>
       </c>
       <c r="F92" s="29">
         <f>เงินสะสมรายเดือน!G15</f>
-        <v>32577549.809999999</v>
+        <v>29351669.179999992</v>
       </c>
       <c r="G92" s="29">
         <f>เงินสะสมรายเดือน!I15</f>
-        <v>166243409.19</v>
+        <v>172910115.14999998</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.25">
